--- a/daily_matches/job_matches_2026-09-30.xlsx
+++ b/daily_matches/job_matches_2026-09-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Systems Engineer, SME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VTG Defense</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Redshift, Synapse, Kinesis, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Redshift, Kafka</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, BigQuery, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b290da3929fa0b4</t>
+          <t>https://www.indeed.com/viewjob?jk=402992014bd3bfa3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr AI/ML Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Pittsburg, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Redshift, BigQuery, Synapse, Git, Snowflake, Databricks, BigQuery</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8788c118957a8b6</t>
+          <t>https://www.indeed.com/viewjob?jk=da5656fa0a41712d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Backend Software Engineer II – AWS &amp; Data Platforms</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, FastAPI, CI/CD, Terraform, Git, PySpark, Kafka</t>
+          <t>Generative AI, LangChain, RAG, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b1c49163f9df6e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ab467c318fd6c96</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI-Native Development Platform Engineer Intern, MS - Summer 2027</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Signant Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, PostgreSQL</t>
+          <t>RAG, Cortex, S3, Glue, Kinesis, CI/CD, Terraform, Git, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ceb60ceb5f3d080b</t>
+          <t>https://www.indeed.com/viewjob?jk=7f8cf55805f4851f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Architect – Client &amp; Technical Solutions</t>
+          <t>Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>arrivia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, FastAPI, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, NoSQL</t>
+          <t>Data Scientist, Synapse, Dataflow, CI/CD, Git, Databricks, PySpark, Kafka, Power BI, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a2398bae43cfca4</t>
+          <t>https://www.indeed.com/viewjob?jk=53d44b35a8a09b64</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Infrastructure Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Upstart</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Snowflake, Databricks</t>
+          <t>RAG, Hugging Face, PyTorch, MLflow, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed859e450f4fb1f8</t>
+          <t>https://www.indeed.com/viewjob?jk=6fb706820b4a71cf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Artificial Intelligence (AI) Research Scientist On-Call</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>California Baptist University</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Riverside, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Cortex, Synapse, Data Lake, CI/CD, GitHub Actions, Git, Snowflake, Python</t>
+          <t>Data Scientist, LangChain, RAG, LLaMA, Gemini, Mistral, TensorFlow, PyTorch, Python, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70ab61efb1bae2af</t>
+          <t>https://www.indeed.com/viewjob?jk=07f7358e6f2c3ddf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer (.NET &amp; AI)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Sony</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, S3, CI/CD, Git, Snowflake, Power BI, SQL</t>
+          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, Databricks, BigQuery, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52e414c0d177032</t>
+          <t>https://www.indeed.com/viewjob?jk=8df8ec8d0f0b7179</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Developer &amp; Data Engineer</t>
+          <t>Research Scientist I/II - Partnership for Advanced Computing Environment (PACE) (Open Rank)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>WISEcode</t>
+          <t>Georgia Tech</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>LangChain, RAG, LLaMA, PyTorch, MLflow, Docker, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961c34d9312bd45f</t>
+          <t>https://www.indeed.com/viewjob?jk=02352f1c776ff89c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Solution Architect – Solutions and Platform Advisory</t>
+          <t>Sr. Engineer, AI Platform Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trianz</t>
+          <t>Petco</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, BigQuery, Dataflow, Kubernetes, CI/CD, Terraform, Git, BigQuery, Python</t>
+          <t>AI Engineer, Generative AI, RAG, Docker, Kubernetes, CI/CD, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=825c83cc17a2a9e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a6482174fdd0a2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior QA Automation Test Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BigQuery, Dataflow, Kubernetes, CI/CD, Jenkins, Terraform, Git, BigQuery, MySQL, SQL</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,129 +846,129 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38f351aee1da6602</t>
+          <t>https://www.indeed.com/viewjob?jk=f32cdccaa21863c7</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - Cloud and DevOps</t>
+          <t>Senior QA Automation Test Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Zions Bancorporation</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Midvale, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, NoSQL, Python</t>
+          <t>RAG, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b52c9ef8ab310ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a0707c0bb358d3ed</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Security AI DevSecOps Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Regional Finance</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, MLflow, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Athena, CI/CD, Git, Polars, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abda70656eba396b</t>
+          <t>https://www.indeed.com/viewjob?jk=a56f376ca7b71d05</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rotational Development Program - AI &amp; Data</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PennEngineering</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Danboro, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Keras, Git, NoSQL, Tableau, Power BI, Python, SQL, R</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Athena, CI/CD, Git, Polars, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1258841d71ad939</t>
+          <t>https://www.indeed.com/viewjob?jk=24fb262e5bf3f8ce</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Engineer II/III (Claims)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MAPFRE Insurance</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Webster, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Athena, CI/CD, Git, Polars, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b375ce161bec97</t>
+          <t>https://www.indeed.com/viewjob?jk=61a7d53b79a50206</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Backend Engineer (Python / FastAPI</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, FastAPI, Docker, Git, PostgreSQL, Python, SQL, R, Scala, Optimization</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Athena, CI/CD, Git, Polars, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bbf427be1168fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=22e2635985628132</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Internship, AI Software Engineer, Core Infrastructure (Winter/Spring 2027)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,77 +1046,77 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R, Scala</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Athena, CI/CD, Git, Polars, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6633675b82e78d48</t>
+          <t>https://www.indeed.com/viewjob?jk=8f43c89e6485c89c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps &amp; Security Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Synapticure</t>
+          <t>Zscaler</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>Machine Learning Engineer, LangChain, RAG, Athena, CI/CD, Git, Polars, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a07ec12340dd65</t>
+          <t>https://www.indeed.com/viewjob?jk=abff698e3a8b3d3b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>API Architect</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SafelyYou</t>
+          <t>Precision Analytical Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McMinnville, OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Kubernetes, CI/CD, Terraform, Kafka, Python, R, Scala</t>
+          <t>RAG, Docker, CI/CD, Git, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b87640e62e54b64</t>
+          <t>https://www.indeed.com/viewjob?jk=dd324299a23feb72</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Data Scientist - Product</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Camping World</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lincolnshire, IL, US USA</t>
+          <t>Menlo Park, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, AKS, CI/CD, Git, Python, R, Java</t>
+          <t>Data Scientist, Redshift, BigQuery, Snowflake, BigQuery, Redshift, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f36ffb41385fcc27</t>
+          <t>https://www.indeed.com/viewjob?jk=d08ae80f757d86ad</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Enterprise Data Solution Architect</t>
+          <t>Senior Software Engineer, Developer Tools &amp; SDKs</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Harman</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Novi, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Git, Snowflake, Databricks, PySpark, Power BI, SQL, R, Scala</t>
+          <t>Copilot, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,3682 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f79d13cbfcddf00</t>
+          <t>https://www.indeed.com/viewjob?jk=2ed762a7f7392ce8</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>DevOps Engineer (Sunnyvale, CA)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Hewlett Packard Enterprise | HPE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08c1f88ad9ad7f1e</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Enterprise AI Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>California Institute of Technology</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pasadena, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Kubernetes, CI/CD, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d73d8e60dd93765</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Software Engineer (Contractor)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>AVB INC.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Copilot, S3, CI/CD, GitHub Actions, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e7d069964a7fab2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b7345fd078a09269</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ea354f208e02af4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c520f276c71ff8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=588ff08a0b4d74f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Mechanicsburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dd47faab9b7758e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Wichita, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b2596b9756b1ddf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65330e780f914f15</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=af42b2a56f34d04d</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a63847178da2b9b3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bae3e037a99b10fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6395f22f83327151</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14482941491f11b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Arlington Heights, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=009d410e9734c12f</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Rosslyn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2e37bb3eda6d003</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e89f223f2f008378</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba386783a8845330</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3113e6aa7a3fc5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25da7e30ce9c189c</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>10</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de65ca98a85d27fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>10</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c013675549d57d10</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b3760639371e7256</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>10</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dab72a71615141c</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>10</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2639e424afdb4c3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=030532d8f97a652c</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>10</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=494baaf39df980b2</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>10</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5483fc2eda58f87b</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Lansing, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>10</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e09a1de1a7e41b5a</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=87d0385c2cec7455</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a18ba6aabdf7b5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>10</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d38a3b3aae8af834</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>10</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2312902d0c3ab69</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>10</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e6ed27f3d64741d</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>10</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b8360112a3d2b66f</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Des Moines, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>10</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f15ac49c82dbabb0</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bce19689addf1634</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>10</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83ef9d41733ebb5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0987c68e467008b</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Hermitage, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7409a48ac2ddceb8</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=debb666e4b9c08ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e8475c3095092f7</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cd1481298763a590</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9fe9ee9fea2ddfcd</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3442923eaf15c3aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8f8e8534b16cd76</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Memphis, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8501ff98b8deb181</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Midland, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2743b76f0a2529b</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=711d4871037e9898</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f12297a84a60ecd</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a7fd35074d0897e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a1d2f4c31810664</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Birmingham, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a8d3582387bd2f20</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=847327b479e834ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Davenport, IA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=638aa73d258968db</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c28c63fdc01fb0f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=386ff5373540bf5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ff74a9094e55e0f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09346445e9dd55d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65dd7c707023059e</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bd33fc016992749</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PROJECT - Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Huntsville, AL, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Apache Airflow, Git, Snowflake, Databricks, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e7d69cb28d86f8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=286dfca4cf97013b</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53d7fa2fbceb781d</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Tempe, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce8b366f82f307a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a28b70075cdb5df</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=607d54702f56416b</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Rosslyn, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72cc86d36841ad26</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a843028951749c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c0cc9cfdde2c4f66</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=895a5a96dd3a7a6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e694566d133ba6f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45c4a0ab25dab390</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=815e6e7dff42c1a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81f93fa1406b8d51</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8545f01061588d70</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e428acae772deb04</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e964f1d561de4c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=97947ef9f15d4cc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef01b3c2fae7034d</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69468adee7079bc8</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1624c55c9ed8df23</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f496e56ea52e29cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ad7a76a9d686eac</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8622fd00adfee95d</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26220e6a756d1b2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06c6e39b00c699e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9ce223ba57bd220</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ae928b923598a5b</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b510161c8f7ec087</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Product Forward Deployed Engineer (pFDE)-Innovation_Delivery_Transformation</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=296293d41c8b477a</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>FW ACQUISITION INC</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Torrance, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RAG, Cortex, OpenCV, Docker, CI/CD, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef5a0c77e71cc47e</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Mistral, Prompt Engineering, R</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96f71e8de51ab745</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Network Value (Credit)</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Plaid</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, Databricks, Redshift, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4284dca0b2bd4995</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=addd53f040eca347</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aee7fa53e27212b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bf57f798ad056b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2b14adf422ddbc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Delivery Senior Consultant, Data Engineering and Gen AI Conversion Solutions</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, TensorFlow, PyTorch, Keras, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80e1eaedbafa1e79</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Cloud Software Engineer (On-site)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, Terraform, Git, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=faa4e2a92b1f4e69</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Software Engineer Supervisor</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1 Click Logistics</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Sparks, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>S3, CI/CD, Git, MySQL, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6990ab6da1729969</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer - Private Assets</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>MSCI Inc.</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AI Engineer, FastAPI, CI/CD, GitHub Actions, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c792284a28ea25d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Full-Stack Web Developer — Political Technology Startup</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Prompt Engineering, Git, PostgreSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ecbda6996eb2ef1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>AI Agent Engineering &amp; DevSecOps Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Kubernetes, CI/CD, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b281cf2fdef072e5</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-30.xlsx
+++ b/daily_matches/job_matches_2026-09-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5 (Java, Spring, Kafka, CI/CD, AI tools, Glue, RDS, DynamoDB) (Enterprise Platforms Technology )</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>HSO</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Glue, Dataflow, Docker, Kubernetes, CI/CD, Git</t>
+          <t>RAG, Synapse, Data Lake, Dataflow, CI/CD, GitHub Actions, Git, Databricks, Kafka, Power BI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7d57da68f94cf58</t>
+          <t>https://www.indeed.com/viewjob?jk=e4f187ec5e311d0c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Data Engineer 4 (Python/AWS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mercury Insurance Company</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.9</v>
+        <v>15.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Athena, Redshift, Data Lake, Docker, CI/CD, Jenkins</t>
+          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83df52bee4296559</t>
+          <t>https://www.indeed.com/viewjob?jk=24e9bddd262f10a8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer - Asset Management, Investment Data &amp; Reporting</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cutter Associates</t>
+          <t>Symbotic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Cortex, MLflow, Docker, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,19 +566,19 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1aff7f94da1f036f</t>
+          <t>https://www.indeed.com/viewjob?jk=c9b624ac55b1048d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,137 +601,137 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab6a7b4ad7bcf714</t>
+          <t>https://www.indeed.com/viewjob?jk=f93009829f3d48c3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Junior Data Scientist</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8bf3660e9d0adc</t>
+          <t>https://www.indeed.com/viewjob?jk=4bcafdcf3406178d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Junior Data Scientist</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4fe6f701d815419</t>
+          <t>https://www.indeed.com/viewjob?jk=42f96e09cd00ba2a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Databricks, PySpark, Kafka</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97fa3ea752ece8fd</t>
+          <t>https://www.indeed.com/viewjob?jk=6e90f8f843f9c8df</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer 5</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6a88e47fd9a09b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c46e6951d692c8ad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,49 +776,49 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1c8cb0925460a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c84b97e682310fa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e514f15ff0b1be4b</t>
+          <t>https://www.indeed.com/viewjob?jk=8e390912a8e6c29c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer 4</t>
+          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,42 +828,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68101adf03f8ea37</t>
+          <t>https://www.indeed.com/viewjob?jk=c208c5545286f6ca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>BigTime Software</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=202928f0f6bbd46e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a77fbe0b9cb6295</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full-Stack Engineer 5</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efb6e669be8a0fe4</t>
+          <t>https://www.indeed.com/viewjob?jk=9fc695363335c863</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5, Marketing and Messaging Experimentation</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35d91349e906a83d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1f14a64600be043</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e511f8782fe3c8af</t>
+          <t>https://www.indeed.com/viewjob?jk=aea20717521078d7</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be58b82de098119</t>
+          <t>https://www.indeed.com/viewjob?jk=99cdf2d275c509b3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Senior Full Stack AI Product Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,1092 +1056,392 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=033490b67917c738</t>
+          <t>https://www.indeed.com/viewjob?jk=a92dd71dd0fcadab</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (Claude, Node JS, Typescript, Python)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Xplor Technologies</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eab3cde603c13024</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c177120b25e2b8</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Orchestration</t>
+          <t>Senior Full Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hunt Military Communities</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R, Java</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56eaabcd481275c5</t>
+          <t>https://www.indeed.com/viewjob?jk=99b31bf06061c552</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbb69805ce87c47</t>
+          <t>https://www.indeed.com/viewjob?jk=c42d956d4515afe7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Enterprise Platform - Marketing Technology</t>
+          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Hill's Pet Nutrition</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=262784cddca9fe3a</t>
+          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5, Agentic Orchestration</t>
+          <t>Sec Dev Ops Engineer - Level 3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Knox Systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=027c7b87d09a28a2</t>
+          <t>https://www.indeed.com/viewjob?jk=5d015060d64b8aa7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - 4 (Java, Python, AWS)</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Derex Technologies inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, S3, EC2, Glue, CI/CD, Terraform, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429d24776ae7a6f3</t>
+          <t>https://www.indeed.com/viewjob?jk=621931178c25b346</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 5</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.3</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=912f48418021fdb1</t>
+          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 (AWS, Java &amp; Python) (Enterprise Platforms Technology)</t>
+          <t>Data Engineer (Hybrid)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Securian Financial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Snowflake, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145d72b83ab51ca3</t>
+          <t>https://www.indeed.com/viewjob?jk=fc6d3d98a5d4d85e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Full Stack Engineer 4</t>
+          <t>AI Data Engineering Intern</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Forvia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>AI Engineer, RAG, Prompt Engineering, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb4ecef48f64d451</t>
+          <t>https://www.indeed.com/viewjob?jk=24c613320061f519</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4</t>
+          <t>Technology &amp; AI Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Berkshire Hathaway HomeServices-Vermont Realty Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>South Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c395ac66d08c231</t>
+          <t>https://www.indeed.com/viewjob?jk=94963cf705861a62</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4, Agentic Technology</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>NextEra Energy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Hadoop, Tableau, Power BI, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e21b621ca9c3081</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 5</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e10d3d79040b3a8</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Wilmington, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=191b82ee06f13c9f</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Full-stack Engineer 4 (Cloud Operations Resilience Engineering)</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Riverwoods, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38cb7271db1de441</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Engineer, Smart Money Services - Fraud &amp; Financial Risk</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Intuit</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, Keras, NLTK, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e064706a80b6d66</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, Customer Engineering</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>anySCALE</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, R</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22770c69f1c9cf48</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Financial Crimes Risk Senior Data Analyst/Data Scientist</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Rain</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c8b176b683dd749</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Senior Site Reliability Engineer I</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Elsevier</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14a9b042577646d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Engineer, Platform Engineering - AI</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Intercontinental Exchange</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, Kubernetes, GitHub Actions, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e11e9c3a874d0bc4</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer 4 (IC)</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Capital One</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, CI/CD, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dad1e0ea50c71edd</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=155a52c6ccd3ec8c</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Frisco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0b6547443bfa61b</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9378c45b27326844</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Humana</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf4280ff8bc8d95a</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>CA Gen Developer</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Wiz Digital Services</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7da7b97bf95ff5e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Veeva Vault CTMS Consultant</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>WinWire</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>10</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>RAG, Glue, Data Lake, Git, Databricks, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=caeb79ce5b8b8b9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Intern, BS/MS - Summer 2027</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Marvell Technology</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Santa Clara, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, Copilot, Docker, Kubernetes, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24572dd3ab9b6c81</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Data Engineer / Data Analyst</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>NXP Semiconductors</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>10</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>S3, EC2, Glue, Athena, Git, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=43de10da0bbe2c25</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>AI Engineer I - (In Office)</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Ring Power Corporation</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Saint Augustine, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>10</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Copilot, Prompt Engineering, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3acabd336c67712</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>EDA AI/ML Software Intern</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Keysight Technologies</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Calabasas, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>10</v>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Generative AI, TensorFlow, PyTorch, Git, Matplotlib, Python, R, Optimization, Bayesian</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f37dcca90cc32269</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>OGC Global</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, XGBoost, PySpark, Dask, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-09-29</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6372b62380f8ea</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab6141f6f9435c0</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-09-30.xlsx
+++ b/daily_matches/job_matches_2026-09-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>AI Enterprise Architect-2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HSO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>27.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Dataflow, CI/CD, GitHub Actions, Git, Databricks, Kafka, Power BI</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, FAISS, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4f187ec5e311d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=fffe73772f679b5c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer 4 (Python/AWS)</t>
+          <t>IT/AI Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Jacam Catalyst</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Midland, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Snowflake, Databricks, Redshift, MongoDB, Cassandra, NoSQL, Python</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e9bddd262f10a8</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1a2298b4a5d694</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI ML Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Symbotic</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Jenkins, Git, Python</t>
+          <t>Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, AWS SageMaker, S3, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9b624ac55b1048d</t>
+          <t>https://www.indeed.com/viewjob?jk=7821be7fd12fc419</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Data Scientist ADAS Analytics Machine Learning</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Mercedes-Benz Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
+          <t>Data Scientist, RAG, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Synapse, MLflow, FastAPI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,159 +601,159 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93009829f3d48c3</t>
+          <t>https://www.indeed.com/viewjob?jk=64507608c433c446</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Sr. AI/ML Engineer - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bcafdcf3406178d</t>
+          <t>https://www.indeed.com/viewjob?jk=ad0d5a4e180f81fe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Data Platform Engineer, Cybersecurity Operations</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
+          <t>RAG, Redshift, BigQuery, Data Lake, CI/CD, Git, Snowflake, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42f96e09cd00ba2a</t>
+          <t>https://www.indeed.com/viewjob?jk=32ed676bd8243856</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Software Engineer III Core Platform</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
+          <t>Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e90f8f843f9c8df</t>
+          <t>https://www.indeed.com/viewjob?jk=b6d0184975ce5875</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>DevOps Sr Engineer - FinOps</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>DaVita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>El Segundo, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
+          <t>RAG, Athena, BigQuery, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c46e6951d692c8ad</t>
+          <t>https://www.indeed.com/viewjob?jk=48e4c25ad47ec8fe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Senior Applied AI Engineer – Supply Chain</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Terraform, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Pinecone, Docker, Kubernetes, CI/CD, Kafka, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c84b97e682310fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1e5916ba993e4752</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Advisor III, Data &amp; MLOps</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, TensorFlow, PyTorch, CI/CD, Git, Databricks</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e390912a8e6c29c</t>
+          <t>https://www.indeed.com/viewjob?jk=399a462361080234</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Full-stack Engineer 4 - Intelligent Foundations and Experiences (IFX)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Goodie AI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Gemini, Docker, CI/CD, Git, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c208c5545286f6ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e25b8407286ff31d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Gen AI Engineer-2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BigTime Software</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python, SQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,159 +881,159 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a77fbe0b9cb6295</t>
+          <t>https://www.indeed.com/viewjob?jk=caaee63497e16cd8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Gen AI Engineer-2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fc695363335c863</t>
+          <t>https://www.indeed.com/viewjob?jk=09659209af6cff2d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Gen AI Engineer-2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Hugging Face, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1f14a64600be043</t>
+          <t>https://www.indeed.com/viewjob?jk=12cc05d58a93a0d3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>Data Scientist, RAG, Copilot, Kubernetes, Terraform, Git, Snowflake, Kafka, Cassandra, Python</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aea20717521078d7</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ae16726479683f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Data Architect - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Argano</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>Generative AI, RAG, Copilot, Dataflow, CI/CD, Terraform, Git, Databricks, PySpark, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99cdf2d275c509b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2dc9469609f69082</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack AI Product Engineer</t>
+          <t>Junior Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,46 +1042,46 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, Git, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Git, Python</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a92dd71dd0fcadab</t>
+          <t>https://www.indeed.com/viewjob?jk=f8008de210f66ab5</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Data Scientist</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Xplor Technologies</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bridgewater, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Git, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0c177120b25e2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=304dd5b968d52a69</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hunt Military Communities</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Python, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, Hugging Face, TensorFlow, PyTorch, AWS SageMaker, Git, Python</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99b31bf06061c552</t>
+          <t>https://www.indeed.com/viewjob?jk=e1e98e3870a81183</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer I</t>
+          <t>BI Developer &amp; Production Support Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Sapta Global</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Cortex, Dataflow, MLflow, CI/CD, Git, Snowflake, Databricks, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c42d956d4515afe7</t>
+          <t>https://www.indeed.com/viewjob?jk=f1bbd59742c441b3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer-Wearables &amp; iOT Analytics</t>
+          <t>Cloud Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hill's Pet Nutrition</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, Jenkins, Terraform, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15106eef96842e6a</t>
+          <t>https://www.indeed.com/viewjob?jk=6517ab56c002de37</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sec Dev Ops Engineer - Level 3</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Knox Systems</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Python, R</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, Pinecone, MLflow, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d015060d64b8aa7</t>
+          <t>https://www.indeed.com/viewjob?jk=3aaf84515bf65e0a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DataOps Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Derex Technologies inc</t>
+          <t>Rubrik</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, CI/CD, Terraform, PySpark, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Pinecone, TensorFlow, PyTorch, AWS SageMaker, GCP Vertex AI, Git</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621931178c25b346</t>
+          <t>https://www.indeed.com/viewjob?jk=250e9fef4a689ff3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>RelMap Software</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>15.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, Cassandra, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Apache Airflow, CI/CD, GitHub Actions, Git, Snowflake, PostgreSQL, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a5b1e38f7c9f340</t>
+          <t>https://www.indeed.com/viewjob?jk=d0c20ad72a268b77</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer (Hybrid)</t>
+          <t>GenAI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Snowflake, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc6d3d98a5d4d85e</t>
+          <t>https://www.indeed.com/viewjob?jk=50f4411af121af4b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AI Data Engineering Intern</t>
+          <t>Gen AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Forvia</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Git, Power BI, Python, SQL, R, Java</t>
+          <t>AI Engineer, Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, FAISS, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24c613320061f519</t>
+          <t>https://www.indeed.com/viewjob?jk=115b0c85f757c61b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Technology &amp; AI Intern</t>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Berkshire Hathaway HomeServices-Vermont Realty Group</t>
+          <t>FCT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>South Burlington, VT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>15.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,42 +1406,3227 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94963cf705861a62</t>
+          <t>https://www.indeed.com/viewjob?jk=ecb1f94893c5712e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Full Stack Senior Software Engineer (Remote in CA)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FCT</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Santa Ana, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, MongoDB, NoSQL, Python</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e0615045d00daaed</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Conversational BI Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sapta Global</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Cortex, MLflow, CI/CD, Git, Snowflake, Databricks, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb3b71809e4f10b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Applied Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05b34176a47f3821</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Glue, Kinesis, CI/CD, Git, Snowflake, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b97a5e70063530e</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>FullStack AWS AI Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Malvern, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, S3, EC2, Docker, CI/CD, GitHub Actions, Terraform, Git</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ce4cac3eae27ecb</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Software Developer II, Full Stack</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>RS21: A Data Science and Visualization Company</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, S3, Docker, Kubernetes, CI/CD, Terraform, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef586201a69cd35c</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Data Scientist</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NextEra Energy</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Plantation, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Hadoop, Tableau, Power BI, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ab6141f6f9435c0</t>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EverQuote</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Cambridge, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, AWS SageMaker, MLflow, Git, Snowflake, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d0a0d80162ea7af3</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Docker, Kubernetes, PostgreSQL, MongoDB, Cassandra, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=952c926fa8ccfeb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE) - GenAI / Agentic AI</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, BigQuery, BigQuery, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b97e3e5ffc449b25</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE) - GenAI / Agentic AI</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, BigQuery, BigQuery, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a796eda31a097fec</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE) - GenAI / Agentic AI</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, BigQuery, BigQuery, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e283de990f937525</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Forward Deployed Engineer (FDE) - GenAI / Agentic AI</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, BigQuery, BigQuery, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8eda034049c5bb0e</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Databricks Engineer - Contract (contract)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>KPMG</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, Snowflake, Databricks, PySpark, Kafka, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0e29091a2e4371e</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Engineer ADAS Fleet Analytics</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mercedes-Benz Group</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, FastAPI, CI/CD, Terraform, Git, Databricks, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11ad6f4a442569a8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Personalization Product Senior Data Associate</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=36a1467311b28d4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2027 Winter Graduate Co-op - Clinical Affairs AI/ML</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Saint Paul, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, XGBoost, LightGBM, Keras, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b62214044e8fc7e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>R&amp;D Machine Analytics</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Trumpf Inc</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Farmington, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, FastAPI, CI/CD, Databricks, PySpark, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9dbb4c6fd5df9e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Data Python Scientist</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Dearborn, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, BigQuery, CI/CD, Git, BigQuery, PostgreSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de0c7dbb1d92bf7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Philip Morris International U.S.</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Synapse, CI/CD, Snowflake, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1f128ebec98d9e3</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Full-stack Engineer 5 (Python, AWS, Typescript)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Capital One</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>McLean, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=91b49f39edeab7ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Senior Java Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BNY</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, Git, Snowflake, Kafka, R</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a688612c128f78f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Enterprise Semantic Layer &amp; Ontology Engineer</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Sapta Global</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Copilot, Cortex, MLflow, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=327f8fe14e958d2a</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist - Healthcare Data</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Surescripts</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Prompt Engineering, Git, Snowflake, Databricks, NoSQL, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8603e5a5b208a4df</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>IMG Academy</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad035bddd06542e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>NCSA College Recruiting</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=730949159ddc5619</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>IMG Academy</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c73326af3eb8dfe5</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Fullstack Engineer, Marketing</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NCSA College Recruiting</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, Docker, CI/CD, Git, MySQL, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7df313ae793a47b9</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>All IT Solutions LLC</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>RAG, Git, Databricks, PySpark, Kafka, Hadoop, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b314fa156cc950c</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Katalyst Healthcares &amp; Life Sciences</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Santa Clara, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Docker, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47286212c4ebf25f</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Threat &amp; Exposure Management Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Git, Kafka, NoSQL, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=35d05800edeb9ae7</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Dynatrace Consultant – Professional Services</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cbd30fca3b2ed50b</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Analyst/Sr Analyst, Revenue Management Development</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Fort Worth, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16b6675dea1446e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Data Engineer / Data Platform Engineer Internship Spring 2027 Semester at the Dow Delivery Center at UIUC (Champaign, IL)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>DOW</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Kankakee, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Terraform, Git, Snowflake, Databricks, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2fea70543399a83d</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Business Systems Engineer – Finance (Temporary)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Matson</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Gemini, Copilot, Git, Power BI, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa5d7948d6bb9015</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Databricks Architect / Drilling &amp; Energy Domain (Contract &amp; FTE)-4</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Tulsa, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Data Lake, MLflow, Databricks, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=07d76e817842815f</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Southern Hobby Distribution</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Cortex, S3, CI/CD, Jenkins, GitHub Actions, Git, Snowflake, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d102e066fd479ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Software Engineer - (Hybrid - Herndon, VA)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Serco</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>RAG, S3, Redshift, Redshift, Power BI, Quicksight, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d93ca2a2bbf3b643</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Git, Databricks, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de53f53ff5d0d5b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>AI and Software Solutions Architect (Remote, Contract)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>INFUSE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MD, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, AKS, Kafka, PostgreSQL, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdfbdeb14e9a28d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Data Engineer-Wearables &amp; iOT Analytics (176270)</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Colgate-Palmolive</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Topeka, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Git, Snowflake, BigQuery, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b5d615a2b140cb52</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>AI Feature &amp; Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Murphy USA</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Databricks, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0119064dd7bc7eec</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Engineer, Machine Learning (All Levels / All Teams)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>DoorDash</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, LightGBM, Keras, Git, Snowflake, PySpark, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05f3cfaeb14918d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Software Engineer III (Python/AWS)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Docker, Kubernetes, CI/CD, Kafka, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ae9297315fd6703</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer (9976) – Department of Technology</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>City and County of San Francisco</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Docker, CI/CD, Jenkins, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14912f1ddd2a23b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Quality Engineering Analyst (Hybrid)</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Intact Insurance Specialty Solutions</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Canton, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38d1f3f905836fd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NLign Analytics</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Blue Ash, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02b2bea570451fe9</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>ML Engineer– Drug Discovery &amp; R&amp;D Operations</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Elanco</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>RAG, TensorFlow, PyTorch, OpenCV, Git, Databricks, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=adcd304fb4e2ecce</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Database Developer - C13</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Citi</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>RAG, Git, PostgreSQL, MySQL, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75576932f59b7e13</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f46f7b35d73a863</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad983b37867da364</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f5114790007f6e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Springfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f4773392276dfb5</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5bae978adf709662</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cef172ec08ca84e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1c54e55784eddd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73d97e5e17e97e7d</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Fort Wayne, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78360ccd758aae8e</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d6af1b4e74b734f</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>The Woodlands, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=282522479edaf7d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29a0f26489404b33</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>South Bend, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84be6d86ec78b7c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eb157aa3757ee5d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Boca Raton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=09908e5dc98f98e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16bc9f408ee0f72f</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4eeb68560df3c1a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Sarasota, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=94a56e35b8adbb02</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=124eaf56202cf76c</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Grand Rapids, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41b14c5042da2785</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ad253596d7e290d</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Livingston, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a6406e374ad222e</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Oakbrook Terrace, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d4fe20ac1b1a474</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Tallahassee, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aacce974d81c5753</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f848dd26d8ae37c</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2acca2695d9ff87d</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3097e704d50aeede</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6f9fbbb3b8f37c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=43a69dfa7f3c4c2e</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Lexington, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=05e40dd112cf87d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a550f7c95ddda531</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c1fc5a15f1556922</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Burlington, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ed964a0e9e7b028</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4a6e4a3f50261288</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db58a155cefe7754</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Crowe</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, Copilot, Prompt Engineering, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6611998986493c71</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Software and Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Simons Foundation</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RAG, PyTorch, Docker, Kubernetes, Git, Python, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4304ec6276e0699</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Primoris Services Corporation</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc7936402a1add06</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Capture)</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Pindrop</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Kafka, R, Scala</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b105d5c5a9f6eb2</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Brookfield Properties</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RAG, Redshift, Git, Redshift, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b6d71d6a76e12d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>METx D&amp;A Intern</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>MetLife</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Cary, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Generative AI, Git, Databricks, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ff1431614a9382c</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d62003cb9f83aeb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e1aa4380989d8a52</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>DevOps Forward Deployed Engineer Job Description (AI &amp; Cloud)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Revstar</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>FL, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RAG, S3, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2b84f726efca9029</t>
         </is>
       </c>
     </row>
